--- a/2025/IDL/Tps/Tp2/planteo_logica.xlsx
+++ b/2025/IDL/Tps/Tp2/planteo_logica.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joaquin\Documents\GitHub\Ing-Computacion\2025\IDL\Tps\Tp2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D16279CC-EAF0-4F31-A1A5-4739D0D1AB71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C167086F-767E-4C9C-B8B6-0BB58C3DAF07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{A3851164-1E18-4C62-B2F7-645213ABECED}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="41">
   <si>
     <t>Estado</t>
   </si>
@@ -272,7 +272,7 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -283,10 +283,19 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -296,15 +305,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -641,7 +641,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA94F4EA-03E9-49EC-9977-32EC667D91A8}">
-  <dimension ref="A1:X10"/>
+  <dimension ref="A1:AB10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="40.6640625" bestFit="1" customWidth="1"/>
@@ -652,9 +652,10 @@
     <col min="11" max="11" width="16" bestFit="1" customWidth="1"/>
     <col min="12" max="14" width="11.77734375" customWidth="1"/>
     <col min="15" max="15" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="19" width="18.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -673,59 +674,71 @@
       <c r="F1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="I1" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="J1" s="14" t="s">
+      <c r="J1" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="K1" s="14" t="s">
+      <c r="K1" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="L1" s="14" t="s">
+      <c r="L1" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="M1" s="14" t="s">
+      <c r="M1" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="N1" s="14" t="s">
+      <c r="N1" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="O1" s="14" t="s">
+      <c r="O1" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="P1" s="15" t="s">
+      <c r="P1" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q1" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="R1" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="S1" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="T1" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="Q1" s="15" t="s">
+      <c r="U1" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="R1" s="15" t="s">
+      <c r="V1" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="S1" s="15" t="s">
+      <c r="W1" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="T1" s="15" t="s">
+      <c r="X1" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="U1" s="15" t="s">
+      <c r="Y1" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="V1" s="15" t="s">
+      <c r="Z1" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="W1" s="15" t="s">
+      <c r="AA1" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="X1" s="15" t="s">
+      <c r="AB1" s="10" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -769,17 +782,17 @@
       <c r="O2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="P2" s="7">
-        <v>1</v>
-      </c>
-      <c r="Q2" s="7">
-        <v>1</v>
-      </c>
-      <c r="R2" s="7">
-        <v>0</v>
-      </c>
-      <c r="S2" s="7">
-        <v>0</v>
+      <c r="P2" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="4">
+        <v>0</v>
+      </c>
+      <c r="R2" s="4">
+        <v>0</v>
+      </c>
+      <c r="S2" s="6" t="s">
+        <v>5</v>
       </c>
       <c r="T2" s="7">
         <v>1</v>
@@ -791,13 +804,25 @@
         <v>0</v>
       </c>
       <c r="W2" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X2" s="7">
         <v>1</v>
       </c>
+      <c r="Y2" s="7">
+        <v>1</v>
+      </c>
+      <c r="Z2" s="7">
+        <v>0</v>
+      </c>
+      <c r="AA2" s="7">
+        <v>1</v>
+      </c>
+      <c r="AB2" s="7">
+        <v>1</v>
+      </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -841,35 +866,47 @@
       <c r="O3" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="P3" s="7">
-        <v>1</v>
-      </c>
-      <c r="Q3" s="7">
-        <v>0</v>
-      </c>
-      <c r="R3" s="7">
-        <v>1</v>
-      </c>
-      <c r="S3" s="7">
-        <v>0</v>
+      <c r="P3" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0</v>
+      </c>
+      <c r="R3" s="4">
+        <v>1</v>
+      </c>
+      <c r="S3" s="6" t="s">
+        <v>6</v>
       </c>
       <c r="T3" s="7">
         <v>1</v>
       </c>
       <c r="U3" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V3" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W3" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X3" s="7">
         <v>1</v>
       </c>
+      <c r="Y3" s="7">
+        <v>1</v>
+      </c>
+      <c r="Z3" s="7">
+        <v>0</v>
+      </c>
+      <c r="AA3" s="7">
+        <v>1</v>
+      </c>
+      <c r="AB3" s="7">
+        <v>1</v>
+      </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -913,26 +950,26 @@
       <c r="O4" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="P4" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="7">
-        <v>1</v>
-      </c>
-      <c r="R4" s="7">
-        <v>1</v>
-      </c>
-      <c r="S4" s="7">
-        <v>1</v>
+      <c r="P4" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>1</v>
+      </c>
+      <c r="R4" s="4">
+        <v>0</v>
+      </c>
+      <c r="S4" s="6" t="s">
+        <v>7</v>
       </c>
       <c r="T4" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U4" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V4" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W4" s="7">
         <v>1</v>
@@ -940,8 +977,20 @@
       <c r="X4" s="7">
         <v>1</v>
       </c>
+      <c r="Y4" s="7">
+        <v>0</v>
+      </c>
+      <c r="Z4" s="7">
+        <v>0</v>
+      </c>
+      <c r="AA4" s="7">
+        <v>1</v>
+      </c>
+      <c r="AB4" s="7">
+        <v>1</v>
+      </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -985,17 +1034,17 @@
       <c r="O5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="P5" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="7">
-        <v>1</v>
-      </c>
-      <c r="R5" s="7">
-        <v>1</v>
-      </c>
-      <c r="S5" s="7">
-        <v>1</v>
+      <c r="P5" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>1</v>
+      </c>
+      <c r="R5" s="4">
+        <v>1</v>
+      </c>
+      <c r="S5" s="6" t="s">
+        <v>8</v>
       </c>
       <c r="T5" s="7">
         <v>0</v>
@@ -1004,16 +1053,28 @@
         <v>1</v>
       </c>
       <c r="V5" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W5" s="7">
         <v>1</v>
       </c>
       <c r="X5" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="7">
+        <v>1</v>
+      </c>
+      <c r="Z5" s="7">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="7">
+        <v>1</v>
+      </c>
+      <c r="AB5" s="7">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -1057,20 +1118,20 @@
       <c r="O6" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="P6" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="7">
-        <v>1</v>
-      </c>
-      <c r="R6" s="7">
-        <v>1</v>
-      </c>
-      <c r="S6" s="7">
-        <v>0</v>
+      <c r="P6" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0</v>
+      </c>
+      <c r="R6" s="4">
+        <v>0</v>
+      </c>
+      <c r="S6" s="6" t="s">
+        <v>9</v>
       </c>
       <c r="T6" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U6" s="7">
         <v>1</v>
@@ -1079,13 +1140,25 @@
         <v>1</v>
       </c>
       <c r="W6" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X6" s="7">
+        <v>1</v>
+      </c>
+      <c r="Y6" s="7">
+        <v>1</v>
+      </c>
+      <c r="Z6" s="7">
+        <v>1</v>
+      </c>
+      <c r="AA6" s="7">
+        <v>1</v>
+      </c>
+      <c r="AB6" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -1129,20 +1202,20 @@
       <c r="O7" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="P7" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="7">
-        <v>1</v>
-      </c>
-      <c r="R7" s="7">
-        <v>1</v>
-      </c>
-      <c r="S7" s="7">
-        <v>0</v>
+      <c r="P7" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0</v>
+      </c>
+      <c r="R7" s="4">
+        <v>1</v>
+      </c>
+      <c r="S7" s="6" t="s">
+        <v>10</v>
       </c>
       <c r="T7" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U7" s="7">
         <v>1</v>
@@ -1156,8 +1229,20 @@
       <c r="X7" s="7">
         <v>1</v>
       </c>
+      <c r="Y7" s="7">
+        <v>1</v>
+      </c>
+      <c r="Z7" s="7">
+        <v>1</v>
+      </c>
+      <c r="AA7" s="7">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="7">
+        <v>1</v>
+      </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.3">
       <c r="H8" s="4">
         <v>1</v>
       </c>
@@ -1182,35 +1267,47 @@
       <c r="O8" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="P8" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q8" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="R8" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="S8" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="T8" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="U8" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="V8" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="W8" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="X8" s="13" t="s">
+      <c r="P8" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>1</v>
+      </c>
+      <c r="R8" s="4">
+        <v>0</v>
+      </c>
+      <c r="S8" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="T8" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="U8" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="V8" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="W8" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="X8" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="Y8" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="Z8" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="AA8" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="AB8" s="8" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.3">
       <c r="H9" s="4">
         <v>1</v>
       </c>
@@ -1235,64 +1332,83 @@
       <c r="O9" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="P9" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q9" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="R9" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="S9" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="T9" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="U9" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="V9" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="W9" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="X9" s="13" t="s">
+      <c r="P9" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="4">
+        <v>1</v>
+      </c>
+      <c r="R9" s="4">
+        <v>1</v>
+      </c>
+      <c r="S9" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="T9" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="U9" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="V9" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="W9" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="X9" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="Y9" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="Z9" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="AA9" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="AB9" s="8" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="H10" s="10" t="s">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="H10" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="I10" s="11"/>
-      <c r="J10" s="11"/>
-      <c r="K10" s="12"/>
-      <c r="L10" s="8" t="s">
+      <c r="I10" s="14"/>
+      <c r="J10" s="14"/>
+      <c r="K10" s="15"/>
+      <c r="L10" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="M10" s="8"/>
-      <c r="N10" s="8"/>
-      <c r="O10" s="8"/>
-      <c r="P10" s="9" t="s">
+      <c r="M10" s="12"/>
+      <c r="N10" s="12"/>
+      <c r="O10" s="12"/>
+      <c r="P10" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q10" s="14"/>
+      <c r="R10" s="14"/>
+      <c r="S10" s="15"/>
+      <c r="T10" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="Q10" s="9"/>
-      <c r="R10" s="9"/>
-      <c r="S10" s="9"/>
-      <c r="T10" s="9"/>
-      <c r="U10" s="9"/>
-      <c r="V10" s="9"/>
-      <c r="W10" s="9"/>
-      <c r="X10" s="9"/>
+      <c r="U10" s="11"/>
+      <c r="V10" s="11"/>
+      <c r="W10" s="11"/>
+      <c r="X10" s="11"/>
+      <c r="Y10" s="11"/>
+      <c r="Z10" s="11"/>
+      <c r="AA10" s="11"/>
+      <c r="AB10" s="11"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="P10:X10"/>
+  <mergeCells count="4">
+    <mergeCell ref="T10:AB10"/>
     <mergeCell ref="L10:O10"/>
     <mergeCell ref="H10:K10"/>
+    <mergeCell ref="P10:S10"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/2025/IDL/Tps/Tp2/planteo_logica.xlsx
+++ b/2025/IDL/Tps/Tp2/planteo_logica.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joaquin\Documents\GitHub\Ing-Computacion\2025\IDL\Tps\Tp2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C167086F-767E-4C9C-B8B6-0BB58C3DAF07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F708F9E-DDF9-416E-9791-9D2252FEAEB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{A3851164-1E18-4C62-B2F7-645213ABECED}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="41">
   <si>
     <t>Estado</t>
   </si>
@@ -128,12 +128,6 @@
     <t>bits de salida (9 kmaps)</t>
   </si>
   <si>
-    <t>NE</t>
-  </si>
-  <si>
-    <t>X</t>
-  </si>
-  <si>
     <t>B4(AS2)</t>
   </si>
   <si>
@@ -159,6 +153,12 @@
   </si>
   <si>
     <t>B0(VS3)</t>
+  </si>
+  <si>
+    <t>S6</t>
+  </si>
+  <si>
+    <t>S7</t>
   </si>
 </sst>
 </file>
@@ -264,7 +264,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -283,9 +283,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -641,7 +638,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA94F4EA-03E9-49EC-9977-32EC667D91A8}">
-  <dimension ref="A1:AB10"/>
+  <dimension ref="A1:X10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="40.6640625" bestFit="1" customWidth="1"/>
@@ -652,10 +649,10 @@
     <col min="11" max="11" width="16" bestFit="1" customWidth="1"/>
     <col min="12" max="14" width="11.77734375" customWidth="1"/>
     <col min="15" max="15" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="16" max="19" width="18.5546875" customWidth="1"/>
+    <col min="16" max="16" width="11.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -674,71 +671,59 @@
       <c r="F1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="J1" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="K1" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="L1" s="9" t="s">
+      <c r="L1" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="M1" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="N1" s="9" t="s">
+      <c r="N1" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="O1" s="9" t="s">
+      <c r="O1" s="8" t="s">
         <v>24</v>
       </c>
       <c r="P1" s="9" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="Q1" s="9" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="R1" s="9" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="S1" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="T1" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="U1" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="V1" s="10" t="s">
+      <c r="T1" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="U1" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="W1" s="10" t="s">
+      <c r="V1" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="X1" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y1" s="10" t="s">
+      <c r="W1" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="Z1" s="10" t="s">
+      <c r="X1" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="AA1" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="AB1" s="10" t="s">
-        <v>40</v>
-      </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -782,17 +767,17 @@
       <c r="O2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="P2" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="4">
-        <v>0</v>
-      </c>
-      <c r="R2" s="4">
-        <v>0</v>
-      </c>
-      <c r="S2" s="6" t="s">
-        <v>5</v>
+      <c r="P2" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="7">
+        <v>1</v>
+      </c>
+      <c r="R2" s="7">
+        <v>1</v>
+      </c>
+      <c r="S2" s="7">
+        <v>0</v>
       </c>
       <c r="T2" s="7">
         <v>1</v>
@@ -801,7 +786,7 @@
         <v>1</v>
       </c>
       <c r="V2" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W2" s="7">
         <v>0</v>
@@ -809,20 +794,8 @@
       <c r="X2" s="7">
         <v>1</v>
       </c>
-      <c r="Y2" s="7">
-        <v>1</v>
-      </c>
-      <c r="Z2" s="7">
-        <v>0</v>
-      </c>
-      <c r="AA2" s="7">
-        <v>1</v>
-      </c>
-      <c r="AB2" s="7">
-        <v>1</v>
-      </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -866,47 +839,35 @@
       <c r="O3" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="P3" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="4">
-        <v>0</v>
-      </c>
-      <c r="R3" s="4">
-        <v>1</v>
-      </c>
-      <c r="S3" s="6" t="s">
-        <v>6</v>
+      <c r="P3" s="7">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="7">
+        <v>1</v>
+      </c>
+      <c r="R3" s="7">
+        <v>0</v>
+      </c>
+      <c r="S3" s="7">
+        <v>0</v>
       </c>
       <c r="T3" s="7">
         <v>1</v>
       </c>
       <c r="U3" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V3" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W3" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X3" s="7">
         <v>1</v>
       </c>
-      <c r="Y3" s="7">
-        <v>1</v>
-      </c>
-      <c r="Z3" s="7">
-        <v>0</v>
-      </c>
-      <c r="AA3" s="7">
-        <v>1</v>
-      </c>
-      <c r="AB3" s="7">
-        <v>1</v>
-      </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -950,26 +911,26 @@
       <c r="O4" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="P4" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="4">
-        <v>1</v>
-      </c>
-      <c r="R4" s="4">
-        <v>0</v>
-      </c>
-      <c r="S4" s="6" t="s">
-        <v>7</v>
+      <c r="P4" s="7">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="7">
+        <v>0</v>
+      </c>
+      <c r="R4" s="7">
+        <v>1</v>
+      </c>
+      <c r="S4" s="7">
+        <v>0</v>
       </c>
       <c r="T4" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U4" s="7">
         <v>1</v>
       </c>
       <c r="V4" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W4" s="7">
         <v>1</v>
@@ -977,20 +938,8 @@
       <c r="X4" s="7">
         <v>1</v>
       </c>
-      <c r="Y4" s="7">
-        <v>0</v>
-      </c>
-      <c r="Z4" s="7">
-        <v>0</v>
-      </c>
-      <c r="AA4" s="7">
-        <v>1</v>
-      </c>
-      <c r="AB4" s="7">
-        <v>1</v>
-      </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -1034,47 +983,35 @@
       <c r="O5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="P5" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="4">
-        <v>1</v>
-      </c>
-      <c r="R5" s="4">
-        <v>1</v>
-      </c>
-      <c r="S5" s="6" t="s">
-        <v>8</v>
+      <c r="P5" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="7">
+        <v>1</v>
+      </c>
+      <c r="R5" s="7">
+        <v>1</v>
+      </c>
+      <c r="S5" s="7">
+        <v>1</v>
       </c>
       <c r="T5" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U5" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V5" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W5" s="7">
         <v>1</v>
       </c>
       <c r="X5" s="7">
-        <v>0</v>
-      </c>
-      <c r="Y5" s="7">
-        <v>1</v>
-      </c>
-      <c r="Z5" s="7">
-        <v>0</v>
-      </c>
-      <c r="AA5" s="7">
-        <v>1</v>
-      </c>
-      <c r="AB5" s="7">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -1118,17 +1055,17 @@
       <c r="O6" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="P6" s="4">
-        <v>1</v>
-      </c>
-      <c r="Q6" s="4">
-        <v>0</v>
-      </c>
-      <c r="R6" s="4">
-        <v>0</v>
-      </c>
-      <c r="S6" s="6" t="s">
-        <v>9</v>
+      <c r="P6" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="7">
+        <v>1</v>
+      </c>
+      <c r="R6" s="7">
+        <v>1</v>
+      </c>
+      <c r="S6" s="7">
+        <v>1</v>
       </c>
       <c r="T6" s="7">
         <v>0</v>
@@ -1137,28 +1074,16 @@
         <v>1</v>
       </c>
       <c r="V6" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W6" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X6" s="7">
         <v>1</v>
       </c>
-      <c r="Y6" s="7">
-        <v>1</v>
-      </c>
-      <c r="Z6" s="7">
-        <v>1</v>
-      </c>
-      <c r="AA6" s="7">
-        <v>1</v>
-      </c>
-      <c r="AB6" s="7">
-        <v>0</v>
-      </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -1202,20 +1127,20 @@
       <c r="O7" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="P7" s="4">
-        <v>1</v>
-      </c>
-      <c r="Q7" s="4">
-        <v>0</v>
-      </c>
-      <c r="R7" s="4">
-        <v>1</v>
-      </c>
-      <c r="S7" s="6" t="s">
-        <v>10</v>
+      <c r="P7" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="7">
+        <v>1</v>
+      </c>
+      <c r="R7" s="7">
+        <v>1</v>
+      </c>
+      <c r="S7" s="7">
+        <v>0</v>
       </c>
       <c r="T7" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U7" s="7">
         <v>1</v>
@@ -1224,25 +1149,13 @@
         <v>1</v>
       </c>
       <c r="W7" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X7" s="7">
-        <v>1</v>
-      </c>
-      <c r="Y7" s="7">
-        <v>1</v>
-      </c>
-      <c r="Z7" s="7">
-        <v>1</v>
-      </c>
-      <c r="AA7" s="7">
-        <v>0</v>
-      </c>
-      <c r="AB7" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
       <c r="H8" s="4">
         <v>1</v>
       </c>
@@ -1253,61 +1166,49 @@
         <v>0</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="L8" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="M8" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="N8" s="5" t="s">
-        <v>31</v>
+        <v>39</v>
+      </c>
+      <c r="L8" s="5">
+        <v>0</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5">
+        <v>0</v>
       </c>
       <c r="O8" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="P8" s="4">
-        <v>1</v>
-      </c>
-      <c r="Q8" s="4">
-        <v>1</v>
-      </c>
-      <c r="R8" s="4">
-        <v>0</v>
-      </c>
-      <c r="S8" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="T8" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="U8" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="V8" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="W8" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="X8" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="Y8" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="Z8" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="AA8" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="AB8" s="8" t="s">
-        <v>31</v>
+        <v>5</v>
+      </c>
+      <c r="P8" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="7">
+        <v>1</v>
+      </c>
+      <c r="R8" s="7">
+        <v>1</v>
+      </c>
+      <c r="S8" s="7">
+        <v>0</v>
+      </c>
+      <c r="T8" s="7">
+        <v>1</v>
+      </c>
+      <c r="U8" s="7">
+        <v>1</v>
+      </c>
+      <c r="V8" s="7">
+        <v>1</v>
+      </c>
+      <c r="W8" s="7">
+        <v>0</v>
+      </c>
+      <c r="X8" s="7">
+        <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
       <c r="H9" s="4">
         <v>1</v>
       </c>
@@ -1318,97 +1219,78 @@
         <v>1</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="L9" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="M9" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="N9" s="5" t="s">
-        <v>31</v>
+        <v>40</v>
+      </c>
+      <c r="L9" s="5">
+        <v>0</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0</v>
+      </c>
+      <c r="N9" s="5">
+        <v>0</v>
       </c>
       <c r="O9" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="P9" s="4">
-        <v>1</v>
-      </c>
-      <c r="Q9" s="4">
-        <v>1</v>
-      </c>
-      <c r="R9" s="4">
-        <v>1</v>
-      </c>
-      <c r="S9" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="T9" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="U9" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="V9" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="W9" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="X9" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="Y9" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="Z9" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="AA9" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="AB9" s="8" t="s">
-        <v>31</v>
+        <v>5</v>
+      </c>
+      <c r="P9" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="7">
+        <v>1</v>
+      </c>
+      <c r="R9" s="7">
+        <v>1</v>
+      </c>
+      <c r="S9" s="7">
+        <v>0</v>
+      </c>
+      <c r="T9" s="7">
+        <v>1</v>
+      </c>
+      <c r="U9" s="7">
+        <v>1</v>
+      </c>
+      <c r="V9" s="7">
+        <v>1</v>
+      </c>
+      <c r="W9" s="7">
+        <v>0</v>
+      </c>
+      <c r="X9" s="7">
+        <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="H10" s="13" t="s">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="H10" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="I10" s="14"/>
-      <c r="J10" s="14"/>
-      <c r="K10" s="15"/>
-      <c r="L10" s="12" t="s">
+      <c r="I10" s="13"/>
+      <c r="J10" s="13"/>
+      <c r="K10" s="14"/>
+      <c r="L10" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="M10" s="12"/>
-      <c r="N10" s="12"/>
-      <c r="O10" s="12"/>
-      <c r="P10" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q10" s="14"/>
-      <c r="R10" s="14"/>
-      <c r="S10" s="15"/>
-      <c r="T10" s="11" t="s">
+      <c r="M10" s="11"/>
+      <c r="N10" s="11"/>
+      <c r="O10" s="11"/>
+      <c r="P10" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="U10" s="11"/>
-      <c r="V10" s="11"/>
-      <c r="W10" s="11"/>
-      <c r="X10" s="11"/>
-      <c r="Y10" s="11"/>
-      <c r="Z10" s="11"/>
-      <c r="AA10" s="11"/>
-      <c r="AB10" s="11"/>
+      <c r="Q10" s="10"/>
+      <c r="R10" s="10"/>
+      <c r="S10" s="10"/>
+      <c r="T10" s="10"/>
+      <c r="U10" s="10"/>
+      <c r="V10" s="10"/>
+      <c r="W10" s="10"/>
+      <c r="X10" s="10"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="T10:AB10"/>
+  <mergeCells count="3">
+    <mergeCell ref="P10:X10"/>
     <mergeCell ref="L10:O10"/>
     <mergeCell ref="H10:K10"/>
-    <mergeCell ref="P10:S10"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
